--- a/public/templates/template_pelatihan.xlsx
+++ b/public/templates/template_pelatihan.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
